--- a/feedback_surveys/036_learning_analytics_trust_and_transparency_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/036_learning_analytics_trust_and_transparency_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>submission_time_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submission Time</t>
+          <t>Submission Time 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -938,12 +938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_phone_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
+          <t>Contact Phone 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>transparency</t>
+          <t>transparency_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Transparency</t>
+          <t>Transparency 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_submission</t>
+          <t>form_submission_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Form Submission</t>
+          <t>Form Submission 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Date (2)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1220,7 +1220,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>transparency_choices</t>
+          <t>transparency_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>transparency_choices</t>
+          <t>transparency_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
